--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.166.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.166.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -875,7 +875,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.166.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.166.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y53"/>
+  <dimension ref="A1:Y59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -605,16 +605,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L29: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 46 â€” 47</t>
+          <t>L32: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L9: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Answerâ€”Continued.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]159</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]159</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L3: isolated marker/symbol line :: 20</t>
@@ -622,7 +626,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L35: isolated marker/symbol line :: +</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]159</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -653,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>105</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -662,14 +666,10 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L32: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L30: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: APPEARANCE - - â€¢</t>
+          <t>L30: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: APPEARANCE - - •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -681,13 +681,13 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L37: isolated marker/symbol line :: 20</t>
+          <t>L35: isolated marker/symbol line :: +</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr">
         <is>
-          <t>L96: punctuation artifact: repeated periods :: The first proceeding in a suit ..........</t>
+          <t>L30: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: APPEARANCE - - •</t>
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr"/>
@@ -721,14 +721,10 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L40: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 23 â€” 113</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L45: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 22â€”23</t>
+          <t>L65: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -740,13 +736,13 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L39: isolated marker/symbol line :: 21</t>
+          <t>L37: isolated marker/symbol line :: 20</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L109: punctuation artifact: repeated periods :: English authorities, .............................</t>
+          <t>L96: punctuation artifact: repeated periods :: The first proceeding in a suit ..........</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
@@ -780,14 +776,10 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L112: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 21 â€” 22</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . 46â€”47</t>
+          <t>L77: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -799,13 +791,13 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L43: isolated marker/symbol line :: 22</t>
+          <t>L39: isolated marker/symbol line :: 21</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr">
         <is>
-          <t>L166: punctuation artifact: repeated periods :: plemental Bills, ...........................</t>
+          <t>L109: punctuation artifact: repeated periods :: English authorities, .............................</t>
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr"/>
@@ -839,14 +831,10 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L117: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 22 â€” 23</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L65: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L100: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -858,11 +846,15 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L47: isolated marker/symbol line :: *</t>
+          <t>L43: isolated marker/symbol line :: 22</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
-      <c r="Q6" s="1" t="inlineStr"/>
+      <c r="Q6" s="1" t="inlineStr">
+        <is>
+          <t>L166: punctuation artifact: repeated periods :: plemental Bills, ...........................</t>
+        </is>
+      </c>
       <c r="R6" s="1" t="inlineStr"/>
       <c r="S6" s="1" t="inlineStr"/>
       <c r="T6" s="1" t="inlineStr"/>
@@ -897,7 +889,7 @@
       <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L75: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 23â€”113</t>
+          <t>L102: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
@@ -909,7 +901,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L49: isolated marker/symbol line :: 44</t>
+          <t>L45: symbol-only separator/garbage line :: 22—23</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -948,7 +940,7 @@
       <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L77: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L187: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
@@ -960,7 +952,7 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L51: isolated marker/symbol line :: 45</t>
+          <t>L47: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -999,7 +991,7 @@
       <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L85: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 31â€”32</t>
+          <t>L189: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
@@ -1011,7 +1003,7 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L53: isolated marker/symbol line :: 46</t>
+          <t>L49: isolated marker/symbol line :: 44</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1033,12 +1025,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1050,7 +1042,7 @@
       <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L86: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 32â€”33</t>
+          <t>L190: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
@@ -1062,7 +1054,7 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L55: isolated marker/symbol line :: 46</t>
+          <t>L51: isolated marker/symbol line :: 45</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1089,7 +1081,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1099,11 +1091,7 @@
       <c r="H11" s="1" t="inlineStr"/>
       <c r="I11" s="1" t="inlineStr"/>
       <c r="J11" s="1" t="inlineStr"/>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L100: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
@@ -1113,7 +1101,7 @@
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L57: isolated marker/symbol line :: 46</t>
+          <t>L53: isolated marker/symbol line :: 46</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1135,12 +1123,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>56</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>58</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1150,21 +1138,17 @@
       <c r="H12" s="1" t="inlineStr"/>
       <c r="I12" s="1" t="inlineStr"/>
       <c r="J12" s="1" t="inlineStr"/>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L102: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L31: isolated marker/symbol line :: 47</t>
+          <t>L29: symbol-only separator/garbage line :: 46 — 47</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L61: isolated marker/symbol line :: 47</t>
+          <t>L55: isolated marker/symbol line :: 46</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1191,7 +1175,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr"/>
@@ -1201,21 +1185,17 @@
       <c r="H13" s="1" t="inlineStr"/>
       <c r="I13" s="1" t="inlineStr"/>
       <c r="J13" s="1" t="inlineStr"/>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L126: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 41â€”42</t>
-        </is>
-      </c>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L32: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L31: isolated marker/symbol line :: 47</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L63: symbol-only separator/garbage line :: . 108</t>
+          <t>L57: isolated marker/symbol line :: 46</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1252,21 +1232,17 @@
       <c r="H14" s="1" t="inlineStr"/>
       <c r="I14" s="1" t="inlineStr"/>
       <c r="J14" s="1" t="inlineStr"/>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L170: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 21â€”22</t>
-        </is>
-      </c>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L33: isolated marker/symbol line :: 108</t>
+          <t>L32: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L65: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L59: symbol-only separator/garbage line :: . 46—47</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1303,21 +1279,17 @@
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="1" t="inlineStr"/>
       <c r="J15" s="1" t="inlineStr"/>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L176: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 22â€”23</t>
-        </is>
-      </c>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L34: isolated marker/symbol line :: '</t>
+          <t>L33: isolated marker/symbol line :: 108</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L67: isolated marker/symbol line :: 23</t>
+          <t>L61: isolated marker/symbol line :: 47</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1354,21 +1326,17 @@
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="1" t="inlineStr"/>
       <c r="J16" s="1" t="inlineStr"/>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L187: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L35: isolated marker/symbol line :: 23</t>
+          <t>L34: isolated marker/symbol line :: '</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L69: isolated marker/symbol line :: 23</t>
+          <t>L63: symbol-only separator/garbage line :: . 108</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1405,21 +1373,17 @@
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr"/>
       <c r="J17" s="1" t="inlineStr"/>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L189: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L36: isolated marker/symbol line :: 23</t>
+          <t>L35: isolated marker/symbol line :: 23</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L71: isolated marker/symbol line :: 24</t>
+          <t>L65: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1444,21 +1408,17 @@
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="1" t="inlineStr"/>
       <c r="J18" s="1" t="inlineStr"/>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L190: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L37: isolated marker/symbol line :: 24</t>
+          <t>L36: isolated marker/symbol line :: 23</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L73: isolated marker/symbol line :: 24</t>
+          <t>L67: isolated marker/symbol line :: 23</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1488,12 +1448,12 @@
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L39: isolated marker/symbol line :: 24</t>
+          <t>L37: isolated marker/symbol line :: 24</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L77: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L69: isolated marker/symbol line :: 23</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1523,12 +1483,12 @@
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L41: isolated marker/symbol line :: 110</t>
+          <t>L39: isolated marker/symbol line :: 24</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L84: isolated marker/symbol line :: 31</t>
+          <t>L71: isolated marker/symbol line :: 24</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1558,12 +1518,12 @@
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L42: isolated marker/symbol line :: 40</t>
+          <t>L40: symbol-only separator/garbage line :: 23 — 113</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L100: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L73: isolated marker/symbol line :: 24</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1593,12 +1553,12 @@
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L43: isolated marker/symbol line :: 40</t>
+          <t>L41: isolated marker/symbol line :: 110</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L102: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L75: symbol-only separator/garbage line :: 23—113</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1628,12 +1588,12 @@
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L44: isolated marker/symbol line :: 40</t>
+          <t>L42: isolated marker/symbol line :: 40</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L104: isolated marker/symbol line :: f.</t>
+          <t>L77: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -1663,12 +1623,12 @@
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L45: isolated marker/symbol line :: 41</t>
+          <t>L43: isolated marker/symbol line :: 40</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L111: isolated marker/symbol line :: 110</t>
+          <t>L84: isolated marker/symbol line :: 31</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -1698,12 +1658,12 @@
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L46: isolated marker/symbol line :: 41</t>
+          <t>L44: isolated marker/symbol line :: 40</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L113: symbol-only separator/garbage line :: . 40</t>
+          <t>L85: symbol-only separator/garbage line :: 31—32</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -1733,12 +1693,12 @@
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L47: isolated marker/symbol line :: 41</t>
+          <t>L45: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L114: isolated marker/symbol line :: 40</t>
+          <t>L86: symbol-only separator/garbage line :: 32—33</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -1768,12 +1728,12 @@
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L51: isolated marker/symbol line :: 5</t>
+          <t>L46: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L115: symbol-only separator/garbage line :: . 40</t>
+          <t>L100: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -1803,12 +1763,12 @@
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L52: isolated marker/symbol line :: 0</t>
+          <t>L47: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L117: symbol-only separator/garbage line :: . 41</t>
+          <t>L102: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -1838,12 +1798,12 @@
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L68: isolated marker/symbol line :: Â·</t>
+          <t>L51: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L119: symbol-only separator/garbage line :: .41</t>
+          <t>L104: isolated marker/symbol line :: f.</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -1873,12 +1833,12 @@
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L69: isolated marker/symbol line :: 31</t>
+          <t>L52: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L121: isolated marker/symbol line :: 41</t>
+          <t>L111: isolated marker/symbol line :: 110</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -1908,12 +1868,12 @@
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L70: symbol-only separator/garbage line :: 31-32</t>
+          <t>L68: isolated marker/symbol line :: ·</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L122: symbol-only separator/garbage line :: . 41</t>
+          <t>L113: symbol-only separator/garbage line :: . 40</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -1943,12 +1903,12 @@
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L71: symbol-only separator/garbage line :: 32-33</t>
+          <t>L69: isolated marker/symbol line :: 31</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L124: isolated marker/symbol line :: 41</t>
+          <t>L114: isolated marker/symbol line :: 40</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -1978,12 +1938,12 @@
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L73: isolated marker/symbol line :: 32</t>
+          <t>L70: symbol-only separator/garbage line :: 31-32</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L130: isolated marker/symbol line :: 42</t>
+          <t>L115: symbol-only separator/garbage line :: . 40</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -2013,12 +1973,12 @@
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L74: isolated marker/symbol line :: 155</t>
+          <t>L71: symbol-only separator/garbage line :: 32-33</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L132: symbol-only separator/garbage line :: . 42</t>
+          <t>L117: symbol-only separator/garbage line :: . 41</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
@@ -2048,12 +2008,12 @@
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L75: isolated marker/symbol line :: 18</t>
+          <t>L73: isolated marker/symbol line :: 32</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L134: isolated marker/symbol line :: 43</t>
+          <t>L119: symbol-only separator/garbage line :: .41</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
@@ -2083,12 +2043,12 @@
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L76: isolated marker/symbol line :: 41</t>
+          <t>L74: isolated marker/symbol line :: 155</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>L135: symbol-only separator/garbage line :: . 43</t>
+          <t>L121: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr"/>
@@ -2118,12 +2078,12 @@
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L77: isolated marker/symbol line :: 41</t>
+          <t>L75: isolated marker/symbol line :: 18</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr">
         <is>
-          <t>L139: isolated marker/symbol line :: 43</t>
+          <t>L122: symbol-only separator/garbage line :: . 41</t>
         </is>
       </c>
       <c r="P37" s="1" t="inlineStr"/>
@@ -2153,12 +2113,12 @@
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L78: symbol-only separator/garbage line :: 41-42</t>
+          <t>L76: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
         <is>
-          <t>L143: isolated marker/symbol line :: 32</t>
+          <t>L124: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="P38" s="1" t="inlineStr"/>
@@ -2188,12 +2148,12 @@
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L80: isolated marker/symbol line :: 42</t>
+          <t>L77: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr">
         <is>
-          <t>L145: symbol-only separator/garbage line :: . 155</t>
+          <t>L126: symbol-only separator/garbage line :: 41—42</t>
         </is>
       </c>
       <c r="P39" s="1" t="inlineStr"/>
@@ -2223,12 +2183,12 @@
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L81: isolated marker/symbol line :: 42</t>
+          <t>L78: symbol-only separator/garbage line :: 41-42</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr">
         <is>
-          <t>L147: isolated marker/symbol line :: 18</t>
+          <t>L130: isolated marker/symbol line :: 42</t>
         </is>
       </c>
       <c r="P40" s="1" t="inlineStr"/>
@@ -2258,12 +2218,12 @@
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L82: isolated marker/symbol line :: 43</t>
+          <t>L80: isolated marker/symbol line :: 42</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr">
         <is>
-          <t>L149: isolated marker/symbol line :: 18</t>
+          <t>L132: symbol-only separator/garbage line :: . 42</t>
         </is>
       </c>
       <c r="P41" s="1" t="inlineStr"/>
@@ -2293,12 +2253,12 @@
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L83: isolated marker/symbol line :: 43</t>
+          <t>L81: isolated marker/symbol line :: 42</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr">
         <is>
-          <t>L151: isolated marker/symbol line :: 19</t>
+          <t>L134: isolated marker/symbol line :: 43</t>
         </is>
       </c>
       <c r="P42" s="1" t="inlineStr"/>
@@ -2328,12 +2288,12 @@
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L85: isolated marker/symbol line :: 43</t>
+          <t>L82: isolated marker/symbol line :: 43</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr">
         <is>
-          <t>L153: isolated marker/symbol line :: 20</t>
+          <t>L135: symbol-only separator/garbage line :: . 43</t>
         </is>
       </c>
       <c r="P43" s="1" t="inlineStr"/>
@@ -2363,12 +2323,12 @@
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L87: isolated marker/symbol line :: 4</t>
+          <t>L83: isolated marker/symbol line :: 43</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr">
         <is>
-          <t>L174: isolated marker/symbol line :: 22</t>
+          <t>L139: isolated marker/symbol line :: 43</t>
         </is>
       </c>
       <c r="P44" s="1" t="inlineStr"/>
@@ -2398,12 +2358,12 @@
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L88: isolated marker/symbol line :: x</t>
+          <t>L85: isolated marker/symbol line :: 43</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr">
         <is>
-          <t>L178: isolated marker/symbol line :: 23</t>
+          <t>L143: isolated marker/symbol line :: 32</t>
         </is>
       </c>
       <c r="P45" s="1" t="inlineStr"/>
@@ -2433,12 +2393,12 @@
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L100: isolated marker/symbol line :: ,</t>
+          <t>L87: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr">
         <is>
-          <t>L180: isolated marker/symbol line :: 4</t>
+          <t>L145: symbol-only separator/garbage line :: . 155</t>
         </is>
       </c>
       <c r="P46" s="1" t="inlineStr"/>
@@ -2468,12 +2428,12 @@
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L101: isolated marker/symbol line :: 6</t>
+          <t>L88: isolated marker/symbol line :: x</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr">
         <is>
-          <t>L187: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L147: isolated marker/symbol line :: 18</t>
         </is>
       </c>
       <c r="P47" s="1" t="inlineStr"/>
@@ -2503,12 +2463,12 @@
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L103: isolated marker/symbol line :: 18</t>
+          <t>L100: isolated marker/symbol line :: ,</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr">
         <is>
-          <t>L189: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L149: isolated marker/symbol line :: 18</t>
         </is>
       </c>
       <c r="P48" s="1" t="inlineStr"/>
@@ -2538,12 +2498,12 @@
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L104: isolated marker/symbol line :: 19</t>
+          <t>L101: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr">
         <is>
-          <t>L190: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L151: isolated marker/symbol line :: 19</t>
         </is>
       </c>
       <c r="P49" s="1" t="inlineStr"/>
@@ -2573,12 +2533,12 @@
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L105: isolated marker/symbol line :: 20</t>
+          <t>L103: isolated marker/symbol line :: 18</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr">
         <is>
-          <t>L192: isolated marker/symbol line :: -</t>
+          <t>L153: isolated marker/symbol line :: 20</t>
         </is>
       </c>
       <c r="P50" s="1" t="inlineStr"/>
@@ -2608,10 +2568,14 @@
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L110: isolated marker/symbol line :: " 6</t>
-        </is>
-      </c>
-      <c r="O51" s="1" t="inlineStr"/>
+          <t>L104: isolated marker/symbol line :: 19</t>
+        </is>
+      </c>
+      <c r="O51" s="1" t="inlineStr">
+        <is>
+          <t>L170: symbol-only separator/garbage line :: 21—22</t>
+        </is>
+      </c>
       <c r="P51" s="1" t="inlineStr"/>
       <c r="Q51" s="1" t="inlineStr"/>
       <c r="R51" s="1" t="inlineStr"/>
@@ -2639,10 +2603,14 @@
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L115: isolated marker/symbol line :: 22</t>
-        </is>
-      </c>
-      <c r="O52" s="1" t="inlineStr"/>
+          <t>L105: isolated marker/symbol line :: 20</t>
+        </is>
+      </c>
+      <c r="O52" s="1" t="inlineStr">
+        <is>
+          <t>L174: isolated marker/symbol line :: 22</t>
+        </is>
+      </c>
       <c r="P52" s="1" t="inlineStr"/>
       <c r="Q52" s="1" t="inlineStr"/>
       <c r="R52" s="1" t="inlineStr"/>
@@ -2670,10 +2638,14 @@
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L118: isolated marker/symbol line :: 23</t>
-        </is>
-      </c>
-      <c r="O53" s="1" t="inlineStr"/>
+          <t>L110: isolated marker/symbol line :: " 6</t>
+        </is>
+      </c>
+      <c r="O53" s="1" t="inlineStr">
+        <is>
+          <t>L176: symbol-only separator/garbage line :: 22—23</t>
+        </is>
+      </c>
       <c r="P53" s="1" t="inlineStr"/>
       <c r="Q53" s="1" t="inlineStr"/>
       <c r="R53" s="1" t="inlineStr"/>
@@ -2685,6 +2657,208 @@
       <c r="X53" s="1" t="inlineStr"/>
       <c r="Y53" s="1" t="inlineStr"/>
     </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr"/>
+      <c r="B54" s="1" t="inlineStr"/>
+      <c r="C54" s="1" t="inlineStr"/>
+      <c r="D54" s="1" t="inlineStr"/>
+      <c r="E54" s="1" t="inlineStr"/>
+      <c r="F54" s="1" t="inlineStr"/>
+      <c r="G54" s="1" t="inlineStr"/>
+      <c r="H54" s="1" t="inlineStr"/>
+      <c r="I54" s="1" t="inlineStr"/>
+      <c r="J54" s="1" t="inlineStr"/>
+      <c r="K54" s="1" t="inlineStr"/>
+      <c r="L54" s="1" t="inlineStr"/>
+      <c r="M54" s="1" t="inlineStr"/>
+      <c r="N54" s="1" t="inlineStr">
+        <is>
+          <t>L112: symbol-only separator/garbage line :: 21 — 22</t>
+        </is>
+      </c>
+      <c r="O54" s="1" t="inlineStr">
+        <is>
+          <t>L178: isolated marker/symbol line :: 23</t>
+        </is>
+      </c>
+      <c r="P54" s="1" t="inlineStr"/>
+      <c r="Q54" s="1" t="inlineStr"/>
+      <c r="R54" s="1" t="inlineStr"/>
+      <c r="S54" s="1" t="inlineStr"/>
+      <c r="T54" s="1" t="inlineStr"/>
+      <c r="U54" s="1" t="inlineStr"/>
+      <c r="V54" s="1" t="inlineStr"/>
+      <c r="W54" s="1" t="inlineStr"/>
+      <c r="X54" s="1" t="inlineStr"/>
+      <c r="Y54" s="1" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr"/>
+      <c r="B55" s="1" t="inlineStr"/>
+      <c r="C55" s="1" t="inlineStr"/>
+      <c r="D55" s="1" t="inlineStr"/>
+      <c r="E55" s="1" t="inlineStr"/>
+      <c r="F55" s="1" t="inlineStr"/>
+      <c r="G55" s="1" t="inlineStr"/>
+      <c r="H55" s="1" t="inlineStr"/>
+      <c r="I55" s="1" t="inlineStr"/>
+      <c r="J55" s="1" t="inlineStr"/>
+      <c r="K55" s="1" t="inlineStr"/>
+      <c r="L55" s="1" t="inlineStr"/>
+      <c r="M55" s="1" t="inlineStr"/>
+      <c r="N55" s="1" t="inlineStr">
+        <is>
+          <t>L115: isolated marker/symbol line :: 22</t>
+        </is>
+      </c>
+      <c r="O55" s="1" t="inlineStr">
+        <is>
+          <t>L180: isolated marker/symbol line :: 4</t>
+        </is>
+      </c>
+      <c r="P55" s="1" t="inlineStr"/>
+      <c r="Q55" s="1" t="inlineStr"/>
+      <c r="R55" s="1" t="inlineStr"/>
+      <c r="S55" s="1" t="inlineStr"/>
+      <c r="T55" s="1" t="inlineStr"/>
+      <c r="U55" s="1" t="inlineStr"/>
+      <c r="V55" s="1" t="inlineStr"/>
+      <c r="W55" s="1" t="inlineStr"/>
+      <c r="X55" s="1" t="inlineStr"/>
+      <c r="Y55" s="1" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr"/>
+      <c r="B56" s="1" t="inlineStr"/>
+      <c r="C56" s="1" t="inlineStr"/>
+      <c r="D56" s="1" t="inlineStr"/>
+      <c r="E56" s="1" t="inlineStr"/>
+      <c r="F56" s="1" t="inlineStr"/>
+      <c r="G56" s="1" t="inlineStr"/>
+      <c r="H56" s="1" t="inlineStr"/>
+      <c r="I56" s="1" t="inlineStr"/>
+      <c r="J56" s="1" t="inlineStr"/>
+      <c r="K56" s="1" t="inlineStr"/>
+      <c r="L56" s="1" t="inlineStr"/>
+      <c r="M56" s="1" t="inlineStr"/>
+      <c r="N56" s="1" t="inlineStr">
+        <is>
+          <t>L117: symbol-only separator/garbage line :: 22 — 23</t>
+        </is>
+      </c>
+      <c r="O56" s="1" t="inlineStr">
+        <is>
+          <t>L187: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
+      <c r="P56" s="1" t="inlineStr"/>
+      <c r="Q56" s="1" t="inlineStr"/>
+      <c r="R56" s="1" t="inlineStr"/>
+      <c r="S56" s="1" t="inlineStr"/>
+      <c r="T56" s="1" t="inlineStr"/>
+      <c r="U56" s="1" t="inlineStr"/>
+      <c r="V56" s="1" t="inlineStr"/>
+      <c r="W56" s="1" t="inlineStr"/>
+      <c r="X56" s="1" t="inlineStr"/>
+      <c r="Y56" s="1" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr"/>
+      <c r="B57" s="1" t="inlineStr"/>
+      <c r="C57" s="1" t="inlineStr"/>
+      <c r="D57" s="1" t="inlineStr"/>
+      <c r="E57" s="1" t="inlineStr"/>
+      <c r="F57" s="1" t="inlineStr"/>
+      <c r="G57" s="1" t="inlineStr"/>
+      <c r="H57" s="1" t="inlineStr"/>
+      <c r="I57" s="1" t="inlineStr"/>
+      <c r="J57" s="1" t="inlineStr"/>
+      <c r="K57" s="1" t="inlineStr"/>
+      <c r="L57" s="1" t="inlineStr"/>
+      <c r="M57" s="1" t="inlineStr"/>
+      <c r="N57" s="1" t="inlineStr">
+        <is>
+          <t>L118: isolated marker/symbol line :: 23</t>
+        </is>
+      </c>
+      <c r="O57" s="1" t="inlineStr">
+        <is>
+          <t>L189: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
+      <c r="P57" s="1" t="inlineStr"/>
+      <c r="Q57" s="1" t="inlineStr"/>
+      <c r="R57" s="1" t="inlineStr"/>
+      <c r="S57" s="1" t="inlineStr"/>
+      <c r="T57" s="1" t="inlineStr"/>
+      <c r="U57" s="1" t="inlineStr"/>
+      <c r="V57" s="1" t="inlineStr"/>
+      <c r="W57" s="1" t="inlineStr"/>
+      <c r="X57" s="1" t="inlineStr"/>
+      <c r="Y57" s="1" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr"/>
+      <c r="B58" s="1" t="inlineStr"/>
+      <c r="C58" s="1" t="inlineStr"/>
+      <c r="D58" s="1" t="inlineStr"/>
+      <c r="E58" s="1" t="inlineStr"/>
+      <c r="F58" s="1" t="inlineStr"/>
+      <c r="G58" s="1" t="inlineStr"/>
+      <c r="H58" s="1" t="inlineStr"/>
+      <c r="I58" s="1" t="inlineStr"/>
+      <c r="J58" s="1" t="inlineStr"/>
+      <c r="K58" s="1" t="inlineStr"/>
+      <c r="L58" s="1" t="inlineStr"/>
+      <c r="M58" s="1" t="inlineStr"/>
+      <c r="N58" s="1" t="inlineStr"/>
+      <c r="O58" s="1" t="inlineStr">
+        <is>
+          <t>L190: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
+      <c r="P58" s="1" t="inlineStr"/>
+      <c r="Q58" s="1" t="inlineStr"/>
+      <c r="R58" s="1" t="inlineStr"/>
+      <c r="S58" s="1" t="inlineStr"/>
+      <c r="T58" s="1" t="inlineStr"/>
+      <c r="U58" s="1" t="inlineStr"/>
+      <c r="V58" s="1" t="inlineStr"/>
+      <c r="W58" s="1" t="inlineStr"/>
+      <c r="X58" s="1" t="inlineStr"/>
+      <c r="Y58" s="1" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr"/>
+      <c r="B59" s="1" t="inlineStr"/>
+      <c r="C59" s="1" t="inlineStr"/>
+      <c r="D59" s="1" t="inlineStr"/>
+      <c r="E59" s="1" t="inlineStr"/>
+      <c r="F59" s="1" t="inlineStr"/>
+      <c r="G59" s="1" t="inlineStr"/>
+      <c r="H59" s="1" t="inlineStr"/>
+      <c r="I59" s="1" t="inlineStr"/>
+      <c r="J59" s="1" t="inlineStr"/>
+      <c r="K59" s="1" t="inlineStr"/>
+      <c r="L59" s="1" t="inlineStr"/>
+      <c r="M59" s="1" t="inlineStr"/>
+      <c r="N59" s="1" t="inlineStr"/>
+      <c r="O59" s="1" t="inlineStr">
+        <is>
+          <t>L192: isolated marker/symbol line :: -</t>
+        </is>
+      </c>
+      <c r="P59" s="1" t="inlineStr"/>
+      <c r="Q59" s="1" t="inlineStr"/>
+      <c r="R59" s="1" t="inlineStr"/>
+      <c r="S59" s="1" t="inlineStr"/>
+      <c r="T59" s="1" t="inlineStr"/>
+      <c r="U59" s="1" t="inlineStr"/>
+      <c r="V59" s="1" t="inlineStr"/>
+      <c r="W59" s="1" t="inlineStr"/>
+      <c r="X59" s="1" t="inlineStr"/>
+      <c r="Y59" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
